--- a/centros_costo.xlsx
+++ b/centros_costo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\Miliandry\OneDrive\Desktop\PROYECTO_ALMACEN\Pasantias2026-Proyecto-Almacen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d57f09bfa23d157f/Desktop/PROYECTO_ALMACEN/Pasantias2026-Proyecto-Almacen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB6ECF07-ACE8-4CC7-AA44-42C008E65430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{FB6ECF07-ACE8-4CC7-AA44-42C008E65430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{740473C3-A23F-40F9-B0FB-2A853926FC7D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42E1A1B0-67D2-4E7D-AF4B-E370B3862888}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>NOMBRE</t>
   </si>
@@ -76,6 +76,18 @@
   </si>
   <si>
     <t>TRAN</t>
+  </si>
+  <si>
+    <t>PRESI</t>
+  </si>
+  <si>
+    <t>GER-GEN</t>
+  </si>
+  <si>
+    <t>PLANIF</t>
+  </si>
+  <si>
+    <t>RRHH</t>
   </si>
 </sst>
 </file>
@@ -126,9 +138,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -443,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4DADF99-B561-46D2-9329-69DA8B3F5C23}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" customWidth="1"/>
@@ -460,73 +473,73 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B9" s="1"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B10" s="1"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B11" s="1"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B12" s="1"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B13" s="1"/>
     </row>
@@ -547,6 +560,30 @@
         <v>16</v>
       </c>
       <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
